--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487549_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487549_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9186</v>
+        <v>10.357</v>
       </c>
       <c r="E2" t="n">
-        <v>9.667199999999999</v>
+        <v>8.865</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2514</v>
+        <v>1.492</v>
       </c>
       <c r="G2" t="n">
         <v>8.4953</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7978</v>
+        <v>1.2361</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3933</v>
+        <v>0.5911</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4045</v>
+        <v>0.645</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9412</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6398</v>
+        <v>6.781</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6751</v>
+        <v>2.6985</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9646</v>
+        <v>4.0825</v>
       </c>
       <c r="G3" t="n">
         <v>5.7005</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4622</v>
+        <v>1.6034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5764</v>
+        <v>0.447</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0385</v>
+        <v>1.1564</v>
       </c>
       <c r="V3" t="n">
         <v>1.0438</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6481</v>
+        <v>4.6067</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6331</v>
+        <v>5.3735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.015</v>
+        <v>-0.7667</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3306</v>
+        <v>5.9637</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9813</v>
+        <v>0.7101</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3493</v>
+        <v>5.2536</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9046</v>
+        <v>6.343</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3188</v>
+        <v>1.3882</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5858</v>
+        <v>4.9547</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.574</v>
+        <v>-0.3792</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3375</v>
+        <v>-0.6781</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2366</v>
+        <v>0.2988</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5668</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8843</v>
+        <v>0.4471</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4496</v>
+        <v>-0.2276</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4347</v>
+        <v>0.6747</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W4" t="n">
         <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1007</v>
+        <v>3.4321</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9477</v>
+        <v>2.444</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8469</v>
+        <v>0.9881</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9637</v>
+        <v>4.4731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7101</v>
+        <v>0.9466</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2536</v>
+        <v>3.5265</v>
       </c>
       <c r="J5" t="n">
-        <v>6.343</v>
+        <v>4.7148</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3882</v>
+        <v>2.033</v>
       </c>
       <c r="L5" t="n">
-        <v>4.9547</v>
+        <v>2.6819</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3792</v>
+        <v>-0.2417</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6781</v>
+        <v>-1.0864</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2988</v>
+        <v>0.8446</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5875</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0589</v>
+        <v>0.7216</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6534</v>
+        <v>0.6669</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5946</v>
+        <v>0.0547</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8948</v>
+        <v>3.2375</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1206</v>
+        <v>3.3027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7742</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4731</v>
+        <v>3.3306</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9466</v>
+        <v>1.9813</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5265</v>
+        <v>1.3493</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7148</v>
+        <v>3.9046</v>
       </c>
       <c r="K6" t="n">
-        <v>2.033</v>
+        <v>2.3188</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6819</v>
+        <v>1.5858</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2417</v>
+        <v>-0.574</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0864</v>
+        <v>-0.3375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8446</v>
+        <v>-0.2366</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7626</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1843</v>
+        <v>1.4737</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3435</v>
+        <v>1.1192</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1591</v>
+        <v>0.3545</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.212</v>
+        <v>1.8619</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3289</v>
+        <v>0.0804</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5409</v>
+        <v>1.7815</v>
       </c>
       <c r="G7" t="n">
         <v>5.455</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5219</v>
+        <v>0.1281</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.517</v>
+        <v>-0.1076</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0049</v>
+        <v>0.2357</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1851</v>
+        <v>0.4494</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0235</v>
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2086</v>
+        <v>0.1694</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.491</v>
+        <v>0.4162</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2141</v>
+        <v>-0.721</v>
       </c>
       <c r="I8" t="n">
-        <v>0.723</v>
+        <v>1.1372</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1702</v>
+        <v>0.9423</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3318</v>
+        <v>0.0935</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1617</v>
+        <v>0.8487</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3209</v>
+        <v>-0.5261</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8822</v>
+        <v>-0.8145</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5614</v>
+        <v>0.2885</v>
       </c>
       <c r="P8" t="n">
         <v>0.3917</v>
@@ -1078,28 +1078,28 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.8581</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.317</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7668</v>
+        <v>0.5411</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3329</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0696</v>
+        <v>0.197</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4528</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3832</v>
+        <v>1.1017</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4162</v>
+        <v>-0.491</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.721</v>
+        <v>-1.2141</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1372</v>
+        <v>0.723</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9423</v>
+        <v>-0.1702</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0935</v>
+        <v>-0.3318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8487</v>
+        <v>0.1617</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5261</v>
+        <v>-0.3209</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8145</v>
+        <v>-0.8822</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2885</v>
+        <v>0.5614</v>
       </c>
       <c r="P9" t="n">
         <v>0.3917</v>
@@ -1156,28 +1156,28 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3391</v>
+        <v>0.6293</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4158</v>
+        <v>-0.0306</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7549</v>
+        <v>0.6599</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>R. BLANCO CARBALLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0113</v>
+        <v>-1.0495</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1925</v>
+        <v>-0.5949</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2039</v>
+        <v>-0.4546</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3164</v>
+        <v>-1.361</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0895</v>
+        <v>-0.866</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7731</v>
+        <v>-0.495</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3419</v>
+        <v>-0.6214</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9562</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2981</v>
+        <v>0.0404</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6584</v>
+        <v>-0.7396</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1333</v>
+        <v>-0.2042</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.525</v>
+        <v>-0.5354</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7175</v>
+        <v>0.1156</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8299</v>
+        <v>0.0265</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1123</v>
+        <v>0.0891</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. BLANCO CARBALLO</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3077</v>
+        <v>-1.2557</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7996</v>
+        <v>-0.3191</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5081</v>
+        <v>-0.9366</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.361</v>
+        <v>-0.3164</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.866</v>
+        <v>-1.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.495</v>
+        <v>0.7731</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6214</v>
+        <v>0.3419</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.9562</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0404</v>
+        <v>1.2981</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7396</v>
+        <v>-0.6584</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2042</v>
+        <v>-0.1333</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5354</v>
+        <v>-0.525</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1958</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1426</v>
+        <v>0.4732</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1782</v>
+        <v>0.3182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0356</v>
+        <v>0.155</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8619</v>
+        <v>-1.4968</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7584</v>
+        <v>-1.5538</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1034</v>
+        <v>0.0569</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7489</v>
@@ -1390,13 +1390,13 @@
         <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5047</v>
+        <v>-0.1397</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4752</v>
+        <v>-0.2705</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0295</v>
+        <v>0.1309</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3156</v>
+        <v>-2.4936</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4974</v>
+        <v>0.2928</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8131</v>
+        <v>-2.7863</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1168</v>
@@ -1468,13 +1468,13 @@
         <v>0.5875</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4095</v>
+        <v>0.2316</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.3764</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1716</v>
+        <v>-0.1448</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2166</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.033</v>
+        <v>24.627</v>
       </c>
       <c r="E14" t="n">
-        <v>19.3704</v>
+        <v>19.9644</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6625</v>
+        <v>4.662700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>28.8003</v>
@@ -1528,13 +1528,13 @@
         <v>22.7548</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.4745</v>
+        <v>-4.474500000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-6.0986</v>
       </c>
       <c r="O14" t="n">
-        <v>1.623999999999999</v>
+        <v>1.624</v>
       </c>
       <c r="P14" t="n">
         <v>-6.8546</v>
@@ -1546,10 +1546,10 @@
         <v>13.7092</v>
       </c>
       <c r="S14" t="n">
-        <v>7.184000000000001</v>
+        <v>7.7781</v>
       </c>
       <c r="T14" t="n">
-        <v>2.632</v>
+        <v>3.226</v>
       </c>
       <c r="U14" t="n">
         <v>4.5522</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2283</v>
+        <v>2.3647</v>
       </c>
       <c r="E15" t="n">
         <v>3.0317</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8034</v>
+        <v>-0.6669</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8293</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1364</v>
       </c>
       <c r="T15" t="n">
         <v>0.0882</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0882</v>
+        <v>0.0482</v>
       </c>
       <c r="V15" t="n">
         <v>1.8825</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7161</v>
+        <v>1.5824</v>
       </c>
       <c r="E16" t="n">
         <v>0.4903</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2258</v>
+        <v>1.0921</v>
       </c>
       <c r="G16" t="n">
         <v>0.9383</v>
@@ -1702,13 +1702,13 @@
         <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0056</v>
+        <v>-0.1392</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U16" t="n">
-        <v>0.232</v>
+        <v>0.0984</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6635</v>
+        <v>0.9262</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3007</v>
+        <v>-0.1984</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9643</v>
+        <v>1.1246</v>
       </c>
       <c r="G17" t="n">
         <v>0.3431</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.463</v>
+        <v>-0.2003</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.166</v>
+        <v>-0.0056</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6624</v>
+        <v>0.2531</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8321</v>
+        <v>0.4228</v>
       </c>
       <c r="F18" t="n">
         <v>-0.1697</v>
@@ -1858,10 +1858,10 @@
         <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1717</v>
+        <v>-0.2376</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4446</v>
+        <v>0.0353</v>
       </c>
       <c r="U18" t="n">
         <v>-0.2729</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1904</v>
+        <v>-0.6061</v>
       </c>
       <c r="E19" t="n">
-        <v>1.784</v>
+        <v>1.0677</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5936</v>
+        <v>-1.6738</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1574</v>
@@ -1936,13 +1936,13 @@
         <v>4.1128</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1359</v>
+        <v>-0.6606</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3835</v>
+        <v>-0.3329</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2475</v>
+        <v>-0.3277</v>
       </c>
       <c r="V19" t="n">
         <v>0.0576</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0649</v>
+        <v>-0.8632</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9653</v>
+        <v>0.3513</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0302</v>
+        <v>-1.2145</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2617</v>
@@ -2014,13 +2014,13 @@
         <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3143</v>
+        <v>-0.484</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1764</v>
+        <v>-0.4376</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1379</v>
+        <v>-0.0465</v>
       </c>
       <c r="V20" t="n">
         <v>3.0991</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2852</v>
+        <v>-1.2318</v>
       </c>
       <c r="E21" t="n">
         <v>-0.3564</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9288</v>
+        <v>-0.8754</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6708</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5937</v>
+        <v>-0.5402</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1875</v>
+        <v>-2.2591</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0548</v>
+        <v>0.7638</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1326</v>
+        <v>-3.0229</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2326</v>
@@ -2170,13 +2170,13 @@
         <v>3.1336</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1128</v>
+        <v>-1.1844</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9009</v>
+        <v>-1.0822</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2119</v>
+        <v>-0.1022</v>
       </c>
       <c r="V22" t="n">
         <v>0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.18</v>
+        <v>-3.9486</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0554</v>
+        <v>-0.8507</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1246</v>
+        <v>-3.0979</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9986</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3772</v>
+        <v>-1.1458</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7128</v>
+        <v>-0.5082</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6644</v>
+        <v>-0.6377</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9503</v>
+        <v>-4.8628</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0708</v>
+        <v>-1.1731</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8795</v>
+        <v>-3.6896</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3741</v>
@@ -2326,13 +2326,13 @@
         <v>0.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6178</v>
+        <v>-0.5302</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2682</v>
+        <v>-0.3705</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3496</v>
+        <v>-0.1597</v>
       </c>
       <c r="V24" t="n">
         <v>1.2166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.605</v>
+        <v>-6.1569</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.1759</v>
+        <v>-0.9712</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4291</v>
+        <v>-5.1857</v>
       </c>
       <c r="G25" t="n">
         <v>-4.5123</v>
@@ -2404,13 +2404,13 @@
         <v>1.3709</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8968</v>
+        <v>-0.4488</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5652</v>
+        <v>-0.3605</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3316</v>
+        <v>-0.0882</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6083</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.220800000000001</v>
+        <v>-8.5488</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.752</v>
+        <v>-7.2403</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4688</v>
+        <v>-1.3085</v>
       </c>
       <c r="G26" t="n">
         <v>-8.5564</v>
@@ -2482,13 +2482,13 @@
         <v>2.9377</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7392</v>
+        <v>-1.0672</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3068</v>
+        <v>-0.7952</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4324</v>
+        <v>-0.272</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8837</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-24.033</v>
+        <v>-23.3509</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.662599999999999</v>
+        <v>-4.6625</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.3702</v>
+        <v>-18.6882</v>
       </c>
       <c r="G27" t="n">
         <v>-28.8003</v>
@@ -2560,13 +2560,13 @@
         <v>20.564</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.1842</v>
+        <v>-6.5019</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.5522</v>
+        <v>-4.552300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.6319</v>
+        <v>-1.9497</v>
       </c>
       <c r="V27" t="n">
         <v>5.096699999999999</v>
